--- a/docs/validacion-lecciones-artesanales.xlsx
+++ b/docs/validacion-lecciones-artesanales.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="0. Léeme" sheetId="1" r:id="rId1"/>
-    <sheet name="1. Vocabulario" sheetId="2" r:id="rId2"/>
-    <sheet name="2. Frases" sheetId="3" r:id="rId3"/>
-    <sheet name="3. Ejercicios" sheetId="4" r:id="rId4"/>
-    <sheet name="4. Cómo arma los ejercicios" sheetId="5" r:id="rId5"/>
-    <sheet name="5. Corpus" sheetId="6" r:id="rId6"/>
-    <sheet name="6. Preguntas" sheetId="7" r:id="rId7"/>
+    <sheet name="N1. Diálogos (módulo nuevo)" sheetId="2" r:id="rId2"/>
+    <sheet name="N2. Vocabulario (módulo nuevo)" sheetId="3" r:id="rId3"/>
+    <sheet name="N3. Notas, tareas y preguntas" sheetId="4" r:id="rId4"/>
+    <sheet name="1. Vocabulario" sheetId="5" r:id="rId5"/>
+    <sheet name="2. Frases" sheetId="6" r:id="rId6"/>
+    <sheet name="3. Ejercicios" sheetId="7" r:id="rId7"/>
+    <sheet name="4. Cómo arma los ejercicios" sheetId="8" r:id="rId8"/>
+    <sheet name="5. Corpus" sheetId="9" r:id="rId9"/>
+    <sheet name="6. Preguntas" sheetId="10" r:id="rId10"/>
   </sheets>
 </workbook>
 </file>
@@ -131,7 +134,7 @@
     <row r="2">
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generado el 05 de agosto de 2026 directamente desde el código de la app. Contacto: Lic. Hugo Arnoldo Carranza Alvarado.</t>
+          <t xml:space="preserve">Generado el 06 de agosto de 2026 directamente desde el código de la app. Contacto: Lic. Hugo Arnoldo Carranza Alvarado.</t>
         </is>
       </c>
     </row>
@@ -220,125 +223,460 @@
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las hojas</t>
+          <t xml:space="preserve">EMPIECE POR ACÁ — el módulo nuevo (hojas N1, N2, N3)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Vocabulario</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Las 36 palabras y expresiones que la app enseña, con la página del diccionario donde se verificó cada una.</t>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Es contenido reescrito desde cero con otra estructura: cada lección es una situación con un diálogo, y el vocabulario sale del diálogo en vez de ir suelto. Es lo que se quiere publicar validado. Son pocas líneas y es donde su tiempo rinde más.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Frases</t>
+          <t xml:space="preserve">N1. Diálogos</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las 34 frases completas que aparecen en pantalla. Se distingue entre las copiadas de una fuente y las ARMADAS para un ejercicio: estas últimas son las que más riesgo tienen.</t>
+          <t xml:space="preserve">Las 22 líneas de conversación del módulo 1. Ninguna se inventó: todas son frases atestiguadas, solo se ordenaron. Lo que hay que juzgar es si suenan naturales en ese orden.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Ejercicios</t>
+          <t xml:space="preserve">N2. Vocabulario</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los 178 ejercicios tal como los ve el estudiante, con su respuesta correcta y sus opciones falsas.</t>
+          <t xml:space="preserve">Las 18 palabras del módulo, con su fuente.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. Cómo arma los ejercicios</t>
+          <t xml:space="preserve">N3. Notas y preguntas</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La app no guarda los ejercicios ya hechos: los arma en el momento. Aquí se explica qué decide la máquina y qué no, y se listan los pares de palabras que podrían confundirse.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5. Corpus</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Qué se extrajo del diccionario, cuánto es, y una tabla para estimar qué costaría revisarlo.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">Las explicaciones gramaticales, las tareas, y las preguntas que quedaron abiertas a propósito. La nota cultural de cada lección está VACÍA esperando su respuesta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6. Preguntas</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Las preguntas concretas que quedaron abiertas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El contenido que ya está publicado (hojas 1 a 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Vocabulario</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las 36 palabras y expresiones que la app enseña hoy, con la página del diccionario donde se verificó cada una.</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sobre la columna "Evidencia"</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Frases</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las 34 frases completas que aparecen en pantalla. Se distingue entre las copiadas de una fuente y las ARMADAS para un ejercicio: estas últimas son las que más riesgo tienen.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Directa</t>
+          <t xml:space="preserve">3. Ejercicios</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La forma aparece tal cual en una fuente, con su página.</t>
+          <t xml:space="preserve">Los 178 ejercicios tal como los ve el estudiante, con su respuesta correcta y sus opciones falsas.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivada</t>
+          <t xml:space="preserve">4. Cómo arma los ejercicios</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La forma se construyó aplicando una regla (por ejemplo, ponerle el prefijo "nu-" a una raíz). La regla está atestiguada; esa forma exacta no se encontró escrita. Son las que más necesitan confirmación.</t>
+          <t xml:space="preserve">La app no guarda los ejercicios ya hechos: los arma en el momento. Aquí se explica qué decide la máquina y qué no, y se listan los pares de palabras que podrían confundirse.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5. Corpus</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qué se extrajo del diccionario, cuánto es, y una tabla para estimar qué costaría revisarlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Preguntas</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las preguntas concretas que quedaron abiertas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sobre la columna "Evidencia"</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Directa</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La forma aparece tal cual en una fuente, con su página.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Derivada</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La forma se construyó aplicando una regla (por ejemplo, ponerle el prefijo "nu-" a una raíz). La regla está atestiguada; esa forma exacta no se encontró escrita. Son las que más necesitan confirmación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Sin localizar</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">No se pudo rastrear. Se enseña igual porque venía del material de origen, pero está sin respaldo documentado.</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="78" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preguntas abiertas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N°</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tema</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pregunta</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ortografía</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿La ortografía que usa la app (IRIN: kw, tz, sh, ch) es la que conviene enseñar hoy, o hay otra más aceptada por los hablantes?</t>
+        </is>
+      </c>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Variante</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La app enseña la variante de Witzapan / Santo Domingo de Guzmán, con la regla K→G. ¿Es la decisión correcta para alguien que empieza desde cero?</t>
+        </is>
+      </c>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formas con guion</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El diccionario marca con guion las formas que exigen prefijo. La app las enseña ya prefijadas: Nikpia "yo tengo", Nikuni "yo bebo", Nutukay "mi nombre". ¿Es la manera correcta de presentárselas a un principiante, o conviene enseñar la raíz y el prefijo por separado?</t>
+        </is>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Itukay</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La app usa "Itukay" para "su nombre", derivada por analogía con "Inan: su madre". Esa forma exacta no se encontró escrita. ¿Existe? ¿Se dice así?</t>
+        </is>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Niawa / Shiawa</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La app enseña Niawa como el adiós del que se va y Shiawa como el del que se queda. ¿Es exacto?</t>
+        </is>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eje</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La app enseña "Eje" para "sí" y no se pudo localizar en el diccionario. ¿De dónde viene? ¿Es correcta?</t>
+        </is>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesu datka</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Tesu datka" se enseña como "de nada". No se localizó como unidad. ¿Se usa así?</t>
+        </is>
+      </c>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nunan</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La app enseña "Nunan" = mi mamá. En el corpus, "Nan" aparece como partícula de negación. ¿Son dos palabras distintas? ¿Nunan está bien?</t>
+        </is>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metzti</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Metzti" = luna se verificó en el PDF pero no está en el corpus extraído. ¿Es la forma correcta? ¿Y "Metzi" existe?</t>
+        </is>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frases armadas</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La hoja 2 marca cuáles frases se ARMARON para los ejercicios de ordenar palabras en lugar de copiarse de una fuente. ¿Están bien construidas gramaticalmente?</t>
+        </is>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Audio</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No hay grabaciones: la app usa una voz sintética en español como aproximación, y silencia las palabras con tz, tl y sh porque el sintetizador las deforma. ¿Vale la pena así, o es mejor quitar el audio hasta tener voz de hablante?</t>
+        </is>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orden</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿El orden de las secciones (sonidos → familia → comida → entorno → acciones) tiene sentido pedagógico, o hay una secuencia mejor?</t>
+        </is>
+      </c>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qué falta</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Para que alguien pueda sostener una conversación mínima, ¿qué falta que hoy no está?</t>
+        </is>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Validación</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Qué bloque de la hoja 5 recomendaría hacer primero, y qué costaría?</t>
+        </is>
+      </c>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autoría</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Si el contenido se revisa y se corrige, ¿cómo quiere aparecer acreditado en la app?</t>
+        </is>
+      </c>
+      <c r="D17" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
@@ -346,6 +684,2113 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Módulo 1 "Ne tajpalulis" — las 22 líneas de los diálogos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N°</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lección</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turno</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quién</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Náhuat</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traducción</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidencia</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuente</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Está bien?</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrección propuesta</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comentario</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yek tunal.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buen día.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.19</t>
+        </is>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yek tunal.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buen día.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.19</t>
+        </is>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ken tinemi?</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Cómo estás?</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.19</t>
+        </is>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C6" s="2">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ninemi yek.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estoy bien.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.19</t>
+        </is>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C7" s="2">
+        <v>5</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wan taja?</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Y tú?</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.21</t>
+        </is>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C8" s="2">
+        <v>6</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yek, padiush.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bien, gracias.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.24</t>
+        </is>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preguntar cómo está alguien</t>
+        </is>
+      </c>
+      <c r="C9" s="2">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ken tinemi?</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Cómo estás?</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.19</t>
+        </is>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preguntar cómo está alguien</t>
+        </is>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naja ninemi yek.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yo estoy bien.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.148</t>
+        </is>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preguntar cómo está alguien</t>
+        </is>
+      </c>
+      <c r="C11" s="2">
+        <v>3</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tinemi yek?</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Estás bien?</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.24</t>
+        </is>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preguntar cómo está alguien</t>
+        </is>
+      </c>
+      <c r="C12" s="2">
+        <v>4</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taja tinemi yek.</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tú estás bien.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.190</t>
+        </is>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preguntar cómo está alguien</t>
+        </is>
+      </c>
+      <c r="C13" s="2">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yek, padiush.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bien, gracias.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.24</t>
+        </is>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hablar de varios</t>
+        </is>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naja ninemi yek.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yo estoy bien.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.148</t>
+        </is>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hablar de varios</t>
+        </is>
+      </c>
+      <c r="C15" s="2">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taja tinemi yek.</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tú estás bien.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.190</t>
+        </is>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hablar de varios</t>
+        </is>
+      </c>
+      <c r="C16" s="2">
+        <v>3</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tejemet tinemit yek.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nosotros estamos bien.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.208</t>
+        </is>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hablar de varios</t>
+        </is>
+      </c>
+      <c r="C17" s="2">
+        <v>4</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anmejemet annemit yek.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ustedes están bien.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.25</t>
+        </is>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decir tu nombre</t>
+        </is>
+      </c>
+      <c r="C18" s="2">
+        <v>1</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ken mutukay?</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Cómo te llamas?</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.21</t>
+        </is>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decir tu nombre</t>
+        </is>
+      </c>
+      <c r="C19" s="2">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nutukay Hugo.</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mi nombre es Hugo.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compuesta</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), entrada −Tukay: "Nutukay: Mi nombre" (p.222). El nombre propio es del estudiante; la estructura es la atestiguada.</t>
+        </is>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decir tu nombre</t>
+        </is>
+      </c>
+      <c r="C20" s="2">
+        <v>3</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wan taja?</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Y tú?</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.21</t>
+        </is>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decir tu nombre</t>
+        </is>
+      </c>
+      <c r="C21" s="2">
+        <v>4</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nutukay Sixta.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mi nombre es Sixta.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">compuesta</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), entrada −Tukay (p.222). Ver la línea anterior.</t>
+        </is>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Despedirse</t>
+        </is>
+      </c>
+      <c r="C22" s="2">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Niawa tel.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ya me voy, pues.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.19</t>
+        </is>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Despedirse</t>
+        </is>
+      </c>
+      <c r="C23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shiawa.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adiós (te vas).</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.184</t>
+        </is>
+      </c>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Despedirse</t>
+        </is>
+      </c>
+      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Padiush.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gracias.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.160</t>
+        </is>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:K24"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="0" sqref="I3:I24">
+      <formula1>"Está bien,Hay que cambiarlo,Tengo dudas"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="32" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="7" max="7" width="46" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="10" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Módulo 1 — las 18 palabras que se enseñan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N°</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lección</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Náhuat</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Significado</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pronunciación</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidencia</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuente</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Está bien?</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrección propuesta</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comentario</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yek</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bueno, bien</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">yek</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.254</t>
+        </is>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tunal</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Día, sol</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tu-nal</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.223</t>
+        </is>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teutak</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tarde</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">teu-tak</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.19</t>
+        </is>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tayua</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Noche</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ta-yu-a</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.207</t>
+        </is>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ken</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cómo</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ken</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.110</t>
+        </is>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wan</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wan</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.246</t>
+        </is>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taja</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tú</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ta-ja</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.19</t>
+        </is>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Padiush</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gracias</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pa-diush</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.160</t>
+        </is>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preguntar cómo está alguien</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nemi</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Estar, vivir</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ne-mi</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.153</t>
+        </is>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preguntar cómo está alguien</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naja</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yo</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">na-ja</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.19</t>
+        </is>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hablar de varios</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yaja</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Él, ella</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ya-ja</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.19</t>
+        </is>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hablar de varios</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tejemet</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nosotros</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">te-je-met</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.19</t>
+        </is>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hablar de varios</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anmejemet</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ustedes</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">an-me-je-met</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.19</t>
+        </is>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decir tu nombre</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nutukay</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mi nombre</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nu-tu-kay</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.222 — "Nutukay: Mi nombre"</t>
+        </is>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decir tu nombre</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mutukay</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tu nombre</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mu-tu-kay</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Curso Timumachtikan (King), p.21 — en "Ken mutukay?"</t>
+        </is>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Despedirse</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Niawa</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ya me voy</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ni-a-wa</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.154</t>
+        </is>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Despedirse</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shiawa</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adiós — lo dice quien se queda</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">shi-a-wa</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.184 — "Adiós (dicho por la persona que se queda), vete"</t>
+        </is>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Despedirse</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tel</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pues, entonces</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tel</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">directa</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diccionario YULTAJTAKETZALIS (Pérez &amp; Martínez, 2023), p.210</t>
+        </is>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:J20"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="0" sqref="H3:H20">
+      <formula1>"Está bien,Hay que cambiarlo,Tengo dudas"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="78" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lo que la app EXPLICA y lo que PIDE hacer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las notas gramaticales y las tareas no se pueden verificar contra un diccionario: o son ciertas y útiles, o no lo son. Esta hoja existe para eso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lección</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota teórica</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Es correcta?</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrección</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Un saludo se arma con "Yek" y el momento del día
+Yek significa «bueno». Puesto delante de una parte del día, forma el saludo: Yek tunal (buen día), Yek teutak (buena tarde), Yek tayua (buena noche).
+Fijate en algo del diálogo: quien saluda y quien responde dicen exactamente lo mismo. En náhuat el saludo se devuelve igual, no se cambia.</t>
+        </is>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preguntar cómo está alguien</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ni- es «yo», ti- es «tú»
+Ya oíste tres veces el mismo verbo con distinta cabeza:
+  ni-nemi  →  yo estoy
+  ti-nemi  →  tú estás
+El verbo náhuat no va suelto: lleva pegado adelante quién hace la acción. Por eso «nemi» a secas casi nunca se dice, igual que en español no decimos «estar» cuando queremos decir «estoy».
+Esta es la pieza más importante del idioma y por eso viene de primero.</t>
+        </is>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hablar de varios</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La -t final quiere decir «somos varios»
+Mirá las cuatro frases juntas:
+  Naja ni-nemi       yo estoy
+  Taja ti-nemi       tú estás
+  Tejemet ti-nemi-t  nosotros estamos
+  Anmejemet an-nemi-t  ustedes están
+Dos cosas pasan a la vez: cambia el prefijo de adelante (quién) y aparece una -t al final cuando son varios.
+Ojo con ti-: sirve para «tú» y para «nosotros». Lo que las distingue es esa -t del final.</t>
+        </is>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decir tu nombre</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hay palabras que nunca andan solas
+«Tukay» quiere decir nombre, pero nadie dice «tukay» a secas. Siempre lleva adelante de quién es:
+  nu-tukay  →  mi nombre
+  mu-tukay  →  tu nombre
+El diccionario lo avisa escribiéndola con un guion delante: −Tukay. Ese guion significa «acá falta algo». Pasa con las partes del cuerpo, la familia y varios verbos.
+Es la misma idea de la lección 2: el náhuat pega la información adelante de la palabra, no en palabras sueltas.</t>
+        </is>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Despedirse</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cada quien tiene su despedida
+En español los dos dicen «adiós». En náhuat no:
+  Niawa   lo dice quien SE VA        («ya me voy»)
+  Shiawa  lo dice quien SE QUEDA     («andá, vaya con bien»)
+No son intercambiables. Decir «shiawa» cuando el que se va sos vos es como despedir a alguien que no se está yendo.
+«Tel» se le pega al final para suavizar, como el «pues» salvadoreño: Niawa tel.</t>
+        </is>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lección</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tarea que se le pide al estudiante</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Tiene sentido?</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comentario</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hoy, a la hora que sea, saludá en voz alta como corresponda: tunal, teutak o tayua. Decilo aunque estés solo — lo que importa es que salga la boca, no que haya quien conteste.</t>
+        </is>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preguntar cómo está alguien</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preguntale «Ken tinemi?» a alguien de confianza y explicale qué significa. Enseñar la frase es la forma más rápida de no olvidarla.</t>
+        </is>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hablar de varios</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Escribí las cuatro frases en un papel, en orden, y leelas en voz alta hasta que la -t final te salga sin pensarla.</t>
+        </is>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decir tu nombre</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decí tu propio nombre completo en náhuat: «Nutukay ___». Es la primera frase del curso que dice algo cierto sobre vos.</t>
+        </is>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Despedirse</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La próxima vez que salgas de un lugar, decí «Niawa» al irte. Fijate si te sale la palabra correcta según si te vas o te quedás.</t>
+        </is>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LAS PREGUNTAS — esto es lo que solo usted puede contestar</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cada lección quedó con un hueco a propósito: la nota cultural la escribe quien pertenece a la comunidad. Inventarla sería el error que este módulo existe para no repetir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lección</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pregunta</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Respuesta</t>
+        </is>
+      </c>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludar según la hora</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Se saluda así en Witzapan hoy, o hay otro saludo más usado en la calle? ¿Qué hora marca el paso de tunal a teutak?</t>
+        </is>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preguntar cómo está alguien</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿«Naja ninemi yek» suena natural en una conversación, o el pronombre «naja» solo se usa para enfatizar? ¿Cuándo se dice y cuándo se calla?</t>
+        </is>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hablar de varios</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Se usan «tejemet» y «anmejemet» en el habla diaria de Witzapan o suenan a libro? ¿Hay formas más cortas?</t>
+        </is>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Decir tu nombre</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿«Nutukay Hugo» es la forma natural de presentarse, o se dice de otra manera? ¿Y cómo se responde cuando a uno le preguntan?</t>
+        </is>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Despedirse</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ESTA ES LA MÁS IMPORTANTE DEL MÓDULO. ¿Es exacto que «niawa» lo dice quien se va y «shiawa» quien se queda? La app lo enseña así desde el principio y nunca lo confirmó un hablante.</t>
+        </is>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2099,7 +4544,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -3233,7 +5678,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10605,7 +13050,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -10876,7 +13321,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -11252,288 +13697,4 @@
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="78" customWidth="1"/>
-    <col min="4" max="4" width="55" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preguntas abiertas</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N°</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tema</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pregunta</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Respuesta</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ortografía</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿La ortografía que usa la app (IRIN: kw, tz, sh, ch) es la que conviene enseñar hoy, o hay otra más aceptada por los hablantes?</t>
-        </is>
-      </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Variante</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La app enseña la variante de Witzapan / Santo Domingo de Guzmán, con la regla K→G. ¿Es la decisión correcta para alguien que empieza desde cero?</t>
-        </is>
-      </c>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Formas con guion</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El diccionario marca con guion las formas que exigen prefijo. La app las enseña ya prefijadas: Nikpia "yo tengo", Nikuni "yo bebo", Nutukay "mi nombre". ¿Es la manera correcta de presentárselas a un principiante, o conviene enseñar la raíz y el prefijo por separado?</t>
-        </is>
-      </c>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Itukay</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La app usa "Itukay" para "su nombre", derivada por analogía con "Inan: su madre". Esa forma exacta no se encontró escrita. ¿Existe? ¿Se dice así?</t>
-        </is>
-      </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Niawa / Shiawa</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La app enseña Niawa como el adiós del que se va y Shiawa como el del que se queda. ¿Es exacto?</t>
-        </is>
-      </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eje</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La app enseña "Eje" para "sí" y no se pudo localizar en el diccionario. ¿De dónde viene? ¿Es correcta?</t>
-        </is>
-      </c>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tesu datka</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Tesu datka" se enseña como "de nada". No se localizó como unidad. ¿Se usa así?</t>
-        </is>
-      </c>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nunan</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La app enseña "Nunan" = mi mamá. En el corpus, "Nan" aparece como partícula de negación. ¿Son dos palabras distintas? ¿Nunan está bien?</t>
-        </is>
-      </c>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Metzti</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Metzti" = luna se verificó en el PDF pero no está en el corpus extraído. ¿Es la forma correcta? ¿Y "Metzi" existe?</t>
-        </is>
-      </c>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Frases armadas</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La hoja 2 marca cuáles frases se ARMARON para los ejercicios de ordenar palabras en lugar de copiarse de una fuente. ¿Están bien construidas gramaticalmente?</t>
-        </is>
-      </c>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Audio</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">No hay grabaciones: la app usa una voz sintética en español como aproximación, y silencia las palabras con tz, tl y sh porque el sintetizador las deforma. ¿Vale la pena así, o es mejor quitar el audio hasta tener voz de hablante?</t>
-        </is>
-      </c>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Orden</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿El orden de las secciones (sonidos → familia → comida → entorno → acciones) tiene sentido pedagógico, o hay una secuencia mejor?</t>
-        </is>
-      </c>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Qué falta</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Para que alguien pueda sostener una conversación mínima, ¿qué falta que hoy no está?</t>
-        </is>
-      </c>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Validación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿Qué bloque de la hoja 5 recomendaría hacer primero, y qué costaría?</t>
-        </is>
-      </c>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autoría</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Si el contenido se revisa y se corrige, ¿cómo quiere aparecer acreditado en la app?</t>
-        </is>
-      </c>
-      <c r="D17" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/docs/validacion-lecciones-artesanales.xlsx
+++ b/docs/validacion-lecciones-artesanales.xlsx
@@ -6,12 +6,13 @@
     <sheet name="N1. Diálogos (módulo nuevo)" sheetId="2" r:id="rId2"/>
     <sheet name="N2. Vocabulario (módulo nuevo)" sheetId="3" r:id="rId3"/>
     <sheet name="N3. Notas, tareas y preguntas" sheetId="4" r:id="rId4"/>
-    <sheet name="1. Vocabulario" sheetId="5" r:id="rId5"/>
-    <sheet name="2. Frases" sheetId="6" r:id="rId6"/>
-    <sheet name="3. Ejercicios" sheetId="7" r:id="rId7"/>
-    <sheet name="4. Cómo arma los ejercicios" sheetId="8" r:id="rId8"/>
-    <sheet name="5. Corpus" sheetId="9" r:id="rId9"/>
-    <sheet name="6. Preguntas" sheetId="10" r:id="rId10"/>
+    <sheet name="N4. Lo que falta" sheetId="5" r:id="rId5"/>
+    <sheet name="1. Vocabulario" sheetId="6" r:id="rId6"/>
+    <sheet name="2. Frases" sheetId="7" r:id="rId7"/>
+    <sheet name="3. Ejercicios" sheetId="8" r:id="rId8"/>
+    <sheet name="4. Cómo arma los ejercicios" sheetId="9" r:id="rId9"/>
+    <sheet name="5. Corpus" sheetId="10" r:id="rId10"/>
+    <sheet name="6. Preguntas" sheetId="11" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
@@ -270,125 +271,137 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="4" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N4. Lo que falta</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LA HOJA MÁS ÚTIL SI HAY POCO TIEMPO. Las palabras que la app ya enseña pero que no se pueden pasar al modelo nuevo porque no existe ninguna frase donde se usen en conversación. Una frase corta por palabra desbloquea cada una.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">El contenido que ya está publicado (hojas 1 a 6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Vocabulario</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Las 36 palabras y expresiones que la app enseña hoy, con la página del diccionario donde se verificó cada una.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2. Frases</t>
+          <t xml:space="preserve">1. Vocabulario</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Las 34 frases completas que aparecen en pantalla. Se distingue entre las copiadas de una fuente y las ARMADAS para un ejercicio: estas últimas son las que más riesgo tienen.</t>
+          <t xml:space="preserve">Las 36 palabras y expresiones que la app enseña hoy, con la página del diccionario donde se verificó cada una.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Ejercicios</t>
+          <t xml:space="preserve">2. Frases</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Los 178 ejercicios tal como los ve el estudiante, con su respuesta correcta y sus opciones falsas.</t>
+          <t xml:space="preserve">Las 34 frases completas que aparecen en pantalla. Se distingue entre las copiadas de una fuente y las ARMADAS para un ejercicio: estas últimas son las que más riesgo tienen.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. Cómo arma los ejercicios</t>
+          <t xml:space="preserve">3. Ejercicios</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La app no guarda los ejercicios ya hechos: los arma en el momento. Aquí se explica qué decide la máquina y qué no, y se listan los pares de palabras que podrían confundirse.</t>
+          <t xml:space="preserve">Los 178 ejercicios tal como los ve el estudiante, con su respuesta correcta y sus opciones falsas.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. Corpus</t>
+          <t xml:space="preserve">4. Cómo arma los ejercicios</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qué se extrajo del diccionario, cuánto es, y una tabla para estimar qué costaría revisarlo.</t>
+          <t xml:space="preserve">La app no guarda los ejercicios ya hechos: los arma en el momento. Aquí se explica qué decide la máquina y qué no, y se listan los pares de palabras que podrían confundirse.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5. Corpus</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qué se extrajo del diccionario, cuánto es, y una tabla para estimar qué costaría revisarlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">6. Preguntas</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Las preguntas concretas que quedaron abiertas.</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="B27" s="4" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Sobre la columna "Evidencia"</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Directa</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">La forma aparece tal cual en una fuente, con su página.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Derivada</t>
+          <t xml:space="preserve">Directa</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">La forma se construyó aplicando una regla (por ejemplo, ponerle el prefijo "nu-" a una raíz). La regla está atestiguada; esa forma exacta no se encontró escrita. Son las que más necesitan confirmación.</t>
+          <t xml:space="preserve">La forma aparece tal cual en una fuente, con su página.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Derivada</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La forma se construyó aplicando una regla (por ejemplo, ponerle el prefijo "nu-" a una raíz). La regla está atestiguada; esa forma exacta no se encontró escrita. Son las que más necesitan confirmación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Sin localizar</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">No se pudo rastrear. Se enseña igual porque venía del material de origen, pero está sin respaldo documentado.</t>
         </is>
@@ -400,6 +413,384 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="66" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El corpus extraído del diccionario</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Es una base de datos armada a partir del YULTAJTAKETZALIS. De ella salen las lecciones generadas automáticamente, que hoy están APAGADAS en la app porque nadie las ha revisado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qué contiene</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuánto</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detalle</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Palabras</t>
+        </is>
+      </c>
+      <c r="C5" s="2">
+        <v>1012</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cada una con su traducción, categoría gramatical, tema y la página de donde salió.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frases</t>
+        </is>
+      </c>
+      <c r="C6" s="2">
+        <v>248</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oraciones de ejemplo, la mayoría del propio diccionario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Descomposiciones morfológicas</t>
+        </is>
+      </c>
+      <c r="C7" s="2">
+        <v>805</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cada frase partida en sus piezas (prefijos de sujeto, objeto, posesivos). Se hicieron POR ALINEACIÓN AUTOMÁTICA: son lo menos confiable de todo el corpus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Formas marcadas con guion</t>
+        </is>
+      </c>
+      <c r="C8" s="2">
+        <v>297</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">El diccionario las escribe con guion inicial (−Pia, −Tukay): no van sueltas, exigen prefijo. La app ya las excluye de las lecciones generadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Páginas del diccionario tocadas</t>
+        </is>
+      </c>
+      <c r="C9" s="2">
+        <v>181</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rango 25–256. NO cubre las pp.26–51 (la parte gramatical inicial), y por eso algunas palabras de las lecciones no se pueden rastrear ahí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Palabras por categoría</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuántas</t>
+        </is>
+      </c>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verbos</t>
+        </is>
+      </c>
+      <c r="C12" s="2">
+        <v>428</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sustantivos</t>
+        </is>
+      </c>
+      <c r="C13" s="2">
+        <v>408</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partículas</t>
+        </is>
+      </c>
+      <c r="C14" s="2">
+        <v>102</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjetivos</t>
+        </is>
+      </c>
+      <c r="C15" s="2">
+        <v>67</v>
+      </c>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saludos</t>
+        </is>
+      </c>
+      <c r="C16" s="2">
+        <v>6</v>
+      </c>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Números</t>
+        </is>
+      </c>
+      <c r="C17" s="2">
+        <v>1</v>
+      </c>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Para estimar el costo de validar</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Los bloques van del más útil y barato al más caro. La idea es poder empezar por uno solo, no por todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bloque</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ítems</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qué habría que revisar</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Horas</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costo</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comentario</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A · Lo que la app ya enseña</t>
+        </is>
+      </c>
+      <c r="C22" s="2">
+        <v>70</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las hojas 1 y 2 de este libro: ortografía, significado y naturalidad de las frases.</t>
+        </is>
+      </c>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">B · Palabras del corpus (forma y significado)</t>
+        </is>
+      </c>
+      <c r="C23" s="2">
+        <v>1012</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Está bien escrita? ¿Significa eso? Sin ejemplos ni gramática.</t>
+        </is>
+      </c>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">C · Solo las formas con guion</t>
+        </is>
+      </c>
+      <c r="C24" s="2">
+        <v>297</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirmar cuáles exigen prefijo y con cuál se enseñan. Es el error que más se repitió en la app.</t>
+        </is>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D · Frases del corpus</t>
+        </is>
+      </c>
+      <c r="C25" s="2">
+        <v>248</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">¿Se dicen así? ¿La traducción es fiel?</t>
+        </is>
+      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E · Descomposiciones morfológicas</t>
+        </is>
+      </c>
+      <c r="C26" s="2">
+        <v>805</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lo más caro y lo más delicado: verificar el análisis morfológico automático.</t>
+        </is>
+      </c>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Honorario por hora</t>
+        </is>
+      </c>
+      <c r="C28" s="3"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">← a llenar en la reunión</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modalidad que le acomoda</t>
+        </is>
+      </c>
+      <c r="C29" s="3"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">por hora / por ítem / por bloque cerrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuánto podría avanzar por semana</t>
+        </is>
+      </c>
+      <c r="C30" s="3"/>
+      <c r="D30" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -2795,6 +3186,800 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="7" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="44" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="9" max="9" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Las 17 palabras que bloquean el reemplazo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Para pasar una palabra al modelo nuevo hace falta una frase donde se use de verdad, en primera o segunda persona. El diccionario da muchas frases, pero casi todas son descripciones ("El canasto grande") que no sirven como turno de conversación. Estas se quedaron sin ninguna. Una frase corta y natural por palabra alcanza para desbloquearla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N°</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Náhuat</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Significado en la app</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sec.</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frases en el corpus</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usables</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La única usable, si la hay</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UNA FRASE NATURAL CON ESTA PALABRA</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Traducción</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eje</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sí</t>
+        </is>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesu</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesu datka</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">De nada</t>
+        </is>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tesu ninemi yek</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No estoy bien</t>
+        </is>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nunan</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mi mamá</t>
+        </is>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nutatanoy</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mi abuelo</t>
+        </is>
+      </c>
+      <c r="D9" s="2">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nuteku</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mi papá</t>
+        </is>
+      </c>
+      <c r="D10" s="2">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Piltzín</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Niño / Niña</t>
+        </is>
+      </c>
+      <c r="D11" s="2">
+        <v>2</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Siwat</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mujer</t>
+        </is>
+      </c>
+      <c r="D12" s="2">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Takat</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hombre</t>
+        </is>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nikuni</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yo bebo</t>
+        </is>
+      </c>
+      <c r="D14" s="2">
+        <v>3</v>
+      </c>
+      <c r="E14" s="2">
+        <v>0</v>
+      </c>
+      <c r="F14" s="2">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2">
+        <v>12</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Takwa</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comer</t>
+        </is>
+      </c>
+      <c r="D15" s="2">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2">
+        <v>0</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kwawit</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Árbol / Leña</t>
+        </is>
+      </c>
+      <c r="D16" s="2">
+        <v>4</v>
+      </c>
+      <c r="E16" s="2">
+        <v>3</v>
+      </c>
+      <c r="F16" s="2">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2">
+        <v>14</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metzti</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luna</t>
+        </is>
+      </c>
+      <c r="D17" s="2">
+        <v>4</v>
+      </c>
+      <c r="E17" s="2">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kuchi</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dormir</t>
+        </is>
+      </c>
+      <c r="D18" s="2">
+        <v>5</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2">
+        <v>16</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paki</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reír / Estar feliz</t>
+        </is>
+      </c>
+      <c r="D19" s="2">
+        <v>5</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>17</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yawi</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ir</t>
+        </is>
+      </c>
+      <c r="D20" s="2">
+        <v>5</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Et</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frijol</t>
+        </is>
+      </c>
+      <c r="D21" s="2">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nikmana ne et = Yo cuezo los frijoles (cocino)</t>
+        </is>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nikpia</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yo tengo</t>
+        </is>
+      </c>
+      <c r="D22" s="2">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naja nikpia se almun shiwit = Yo tengo</t>
+        </is>
+      </c>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2">
+        <v>20</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kal</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Casa</t>
+        </is>
+      </c>
+      <c r="D23" s="2">
+        <v>4</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Niktajkwilua se kal = Yo dibujo una casa</t>
+        </is>
+      </c>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2">
+        <v>21</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mistun</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gato</t>
+        </is>
+      </c>
+      <c r="D24" s="2">
+        <v>4</v>
+      </c>
+      <c r="E24" s="2">
+        <v>4</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naja nikalaktia ne mistun = Yo entro al gato</t>
+        </is>
+      </c>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2">
+        <v>22</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pelu</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perro</t>
+        </is>
+      </c>
+      <c r="D25" s="2">
+        <v>4</v>
+      </c>
+      <c r="E25" s="2">
+        <v>9</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nikpashalua ne pelu = Yo paseo al perro</t>
+        </is>
+      </c>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2">
+        <v>23</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">At</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agua</t>
+        </is>
+      </c>
+      <c r="D26" s="2">
+        <v>3</v>
+      </c>
+      <c r="E26" s="2">
+        <v>5</v>
+      </c>
+      <c r="F26" s="2">
+        <v>2</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naja nikumima at = Yo tiro agua (lejos)</t>
+        </is>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
@@ -4544,7 +5729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5678,7 +6863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13050,7 +14235,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -13319,382 +14504,4 @@
   </dataValidations>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="66" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El corpus extraído del diccionario</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Es una base de datos armada a partir del YULTAJTAKETZALIS. De ella salen las lecciones generadas automáticamente, que hoy están APAGADAS en la app porque nadie las ha revisado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Qué contiene</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cuánto</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Detalle</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Palabras</t>
-        </is>
-      </c>
-      <c r="C5" s="2">
-        <v>1012</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cada una con su traducción, categoría gramatical, tema y la página de donde salió.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Frases</t>
-        </is>
-      </c>
-      <c r="C6" s="2">
-        <v>248</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oraciones de ejemplo, la mayoría del propio diccionario.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Descomposiciones morfológicas</t>
-        </is>
-      </c>
-      <c r="C7" s="2">
-        <v>805</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cada frase partida en sus piezas (prefijos de sujeto, objeto, posesivos). Se hicieron POR ALINEACIÓN AUTOMÁTICA: son lo menos confiable de todo el corpus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Formas marcadas con guion</t>
-        </is>
-      </c>
-      <c r="C8" s="2">
-        <v>297</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">El diccionario las escribe con guion inicial (−Pia, −Tukay): no van sueltas, exigen prefijo. La app ya las excluye de las lecciones generadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Páginas del diccionario tocadas</t>
-        </is>
-      </c>
-      <c r="C9" s="2">
-        <v>181</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rango 25–256. NO cubre las pp.26–51 (la parte gramatical inicial), y por eso algunas palabras de las lecciones no se pueden rastrear ahí.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Palabras por categoría</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cuántas</t>
-        </is>
-      </c>
-      <c r="D11" s="1"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verbos</t>
-        </is>
-      </c>
-      <c r="C12" s="2">
-        <v>428</v>
-      </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sustantivos</t>
-        </is>
-      </c>
-      <c r="C13" s="2">
-        <v>408</v>
-      </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Partículas</t>
-        </is>
-      </c>
-      <c r="C14" s="2">
-        <v>102</v>
-      </c>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Adjetivos</t>
-        </is>
-      </c>
-      <c r="C15" s="2">
-        <v>67</v>
-      </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Saludos</t>
-        </is>
-      </c>
-      <c r="C16" s="2">
-        <v>6</v>
-      </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Números</t>
-        </is>
-      </c>
-      <c r="C17" s="2">
-        <v>1</v>
-      </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Para estimar el costo de validar</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Los bloques van del más útil y barato al más caro. La idea es poder empezar por uno solo, no por todo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bloque</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ítems</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Qué habría que revisar</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Horas</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Costo</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Comentario</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A · Lo que la app ya enseña</t>
-        </is>
-      </c>
-      <c r="C22" s="2">
-        <v>70</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Las hojas 1 y 2 de este libro: ortografía, significado y naturalidad de las frases.</t>
-        </is>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B · Palabras del corpus (forma y significado)</t>
-        </is>
-      </c>
-      <c r="C23" s="2">
-        <v>1012</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿Está bien escrita? ¿Significa eso? Sin ejemplos ni gramática.</t>
-        </is>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C · Solo las formas con guion</t>
-        </is>
-      </c>
-      <c r="C24" s="2">
-        <v>297</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Confirmar cuáles exigen prefijo y con cuál se enseñan. Es el error que más se repitió en la app.</t>
-        </is>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">D · Frases del corpus</t>
-        </is>
-      </c>
-      <c r="C25" s="2">
-        <v>248</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">¿Se dicen así? ¿La traducción es fiel?</t>
-        </is>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E · Descomposiciones morfológicas</t>
-        </is>
-      </c>
-      <c r="C26" s="2">
-        <v>805</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lo más caro y lo más delicado: verificar el análisis morfológico automático.</t>
-        </is>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Honorario por hora</t>
-        </is>
-      </c>
-      <c r="C28" s="3"/>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">← a llenar en la reunión</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Modalidad que le acomoda</t>
-        </is>
-      </c>
-      <c r="C29" s="3"/>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">por hora / por ítem / por bloque cerrado</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cuánto podría avanzar por semana</t>
-        </is>
-      </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="2"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
-</worksheet>
 </file>